--- a/plots/countries/sectors/France-sectors.xlsx
+++ b/plots/countries/sectors/France-sectors.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">Author</t>
   </si>
@@ -30,13 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2025). Tidy GHG Inventories (1.0) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14945466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See also</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
@@ -443,14 +437,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -464,79 +450,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>1990</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>82.4923587319877</v>
+        <v>82.750876806839</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>1990</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>102.921183358857</v>
+        <v>102.936419974374</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>1990</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>11.7899157185677</v>
@@ -544,179 +530,179 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>1990</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>64.3450886392835</v>
+        <v>65.4884753708568</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>1990</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>66.3035643858609</v>
+        <v>66.5477840738347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>1990</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>123.224025390385</v>
+        <v>125.038473140041</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>1990</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>75.2821512531811</v>
+        <v>75.1875260614659</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>1990</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>-22.3642982643478</v>
+        <v>-25.8777809692387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>1990</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>18.5568068969435</v>
+        <v>18.7195300745012</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
       <c r="D11" t="n">
         <v>1991</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>81.4074678492541</v>
+        <v>81.729041370146</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>1991</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>112.650220285213</v>
+        <v>112.649247025061</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
         <v>1991</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>11.505073603903</v>
@@ -724,179 +710,179 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
         <v>1991</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>77.3676212121184</v>
+        <v>78.6507145952158</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>1991</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>67.7688255448728</v>
+        <v>68.0303999946692</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>1991</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>125.916534000047</v>
+        <v>127.705481016869</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>1991</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>74.32977181177</v>
+        <v>74.4061474104692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
         <v>1991</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>-22.1042194060263</v>
+        <v>-27.286991706254</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
         <v>1991</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>19.3584262219673</v>
+        <v>19.5290377890703</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>1992</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>80.5481506367021</v>
+        <v>80.8787155145771</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
         <v>1992</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>108.914495815717</v>
+        <v>108.91870865722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
         <v>1992</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>11.6723252056495</v>
@@ -904,179 +890,179 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
         <v>1992</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>67.3035347289419</v>
+        <v>68.6264938296832</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>1992</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>68.8535909590639</v>
+        <v>69.1371455815917</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
         <v>1992</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>130.302101876424</v>
+        <v>132.052475096356</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>1992</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>71.8839553997361</v>
+        <v>71.6964564670548</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>1992</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>-20.5162968938936</v>
+        <v>-27.4667574746483</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
         <v>1992</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>20.1599504894109</v>
+        <v>20.3393415961216</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
       </c>
       <c r="D29" t="n">
         <v>1993</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>79.2873729345991</v>
+        <v>79.6135792045779</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
         <v>1993</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>105.513079159042</v>
+        <v>105.500967036192</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
         <v>1993</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>11.6630086680784</v>
@@ -1084,179 +1070,179 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D32" t="n">
         <v>1993</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>64.4074240286365</v>
+        <v>65.8238780503791</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" t="n">
         <v>1993</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>56.5979378458448</v>
+        <v>56.9289582107272</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
         <v>1993</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
-        <v>130.413085377279</v>
+        <v>132.16080966745</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
         <v>1993</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>69.316300790676</v>
+        <v>69.1991538481619</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D36" t="n">
         <v>1993</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>-24.4709486129535</v>
+        <v>-30.9003182199417</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
         <v>1993</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>20.9539181776927</v>
+        <v>21.1437532512872</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
         <v>14</v>
-      </c>
-      <c r="B38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" t="s">
-        <v>16</v>
       </c>
       <c r="D38" t="n">
         <v>1994</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>78.6233510381284</v>
+        <v>78.9559522200455</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
         <v>1994</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>98.5125431934161</v>
+        <v>98.4946343757167</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D40" t="n">
         <v>1994</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
         <v>12.0180524751534</v>
@@ -1264,179 +1250,179 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D41" t="n">
         <v>1994</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>65.3916469801695</v>
+        <v>66.7466862988681</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D42" t="n">
         <v>1994</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
-        <v>53.0169526883405</v>
+        <v>53.4256444331448</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D43" t="n">
         <v>1994</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>131.3903537091</v>
+        <v>133.078737376967</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
         <v>1994</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
-        <v>69.4369491287157</v>
+        <v>69.4863523445536</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D45" t="n">
         <v>1994</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>-22.4703932024914</v>
+        <v>-28.9089730230256</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D46" t="n">
         <v>1994</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>21.3517525898943</v>
+        <v>21.5351832271482</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
         <v>14</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" t="s">
-        <v>16</v>
       </c>
       <c r="D47" t="n">
         <v>1995</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>79.1461313351663</v>
+        <v>79.5004522684479</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D48" t="n">
         <v>1995</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>97.8998514052355</v>
+        <v>97.9035304375447</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
         <v>1995</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
         <v>11.7793731587355</v>
@@ -1444,179 +1430,179 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D50" t="n">
         <v>1995</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F50" t="n">
-        <v>67.7459093653742</v>
+        <v>69.3428656014005</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
         <v>1995</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F51" t="n">
-        <v>55.7626000201894</v>
+        <v>56.1750033452879</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D52" t="n">
         <v>1995</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F52" t="n">
-        <v>133.317189837669</v>
+        <v>134.982175387261</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D53" t="n">
         <v>1995</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>68.2461748391028</v>
+        <v>68.9292819669851</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D54" t="n">
         <v>1995</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>-25.8044684839677</v>
+        <v>-32.1447620302408</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D55" t="n">
         <v>1995</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>21.6394162408144</v>
+        <v>21.8275953934057</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
         <v>14</v>
-      </c>
-      <c r="B56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" t="s">
-        <v>16</v>
       </c>
       <c r="D56" t="n">
         <v>1996</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
-        <v>79.6953293464819</v>
+        <v>80.0334390543215</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
         <v>1996</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>107.290062134883</v>
+        <v>107.246345104882</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D58" t="n">
         <v>1996</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
         <v>10.5553676973129</v>
@@ -1624,179 +1610,179 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D59" t="n">
         <v>1996</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F59" t="n">
-        <v>69.7749762905619</v>
+        <v>71.288457161132</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D60" t="n">
         <v>1996</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>60.4802287762919</v>
+        <v>60.8840042256803</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D61" t="n">
         <v>1996</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
-        <v>135.105737032394</v>
+        <v>136.831804835123</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D62" t="n">
         <v>1996</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>69.1226485536875</v>
+        <v>69.9127931253853</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D63" t="n">
         <v>1996</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>-33.203094882668</v>
+        <v>-38.5236041735282</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D64" t="n">
         <v>1996</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>21.7051100181792</v>
+        <v>21.8982929188914</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
         <v>14</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" t="s">
-        <v>16</v>
       </c>
       <c r="D65" t="n">
         <v>1997</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>79.7500511810393</v>
+        <v>80.0452820811818</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D66" t="n">
         <v>1997</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>101.813517725518</v>
+        <v>101.770620499138</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D67" t="n">
         <v>1997</v>
       </c>
       <c r="E67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
         <v>9.84324399142234</v>
@@ -1804,179 +1790,179 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D68" t="n">
         <v>1997</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>67.7931806844871</v>
+        <v>69.3881254537726</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
         <v>1997</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>56.9111480355206</v>
+        <v>57.3250799248435</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D70" t="n">
         <v>1997</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>137.604992193471</v>
+        <v>139.306439591129</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
         <v>1997</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
-        <v>70.430969895764</v>
+        <v>71.3691253291766</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D72" t="n">
         <v>1997</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>-34.4723167842663</v>
+        <v>-40.3572278732717</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D73" t="n">
         <v>1997</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>21.7391429451168</v>
+        <v>21.9368288403112</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
         <v>14</v>
-      </c>
-      <c r="B74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" t="s">
-        <v>16</v>
       </c>
       <c r="D74" t="n">
         <v>1998</v>
       </c>
       <c r="E74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F74" t="n">
-        <v>79.6367731639692</v>
+        <v>79.9317524707601</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D75" t="n">
         <v>1998</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
-        <v>106.403633317518</v>
+        <v>106.332580589918</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D76" t="n">
         <v>1998</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F76" t="n">
         <v>9.66281260748395</v>
@@ -1984,179 +1970,179 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D77" t="n">
         <v>1998</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>66.9400202754194</v>
+        <v>68.587287342507</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
         <v>1998</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>69.475188558578</v>
+        <v>69.9102406086612</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D79" t="n">
         <v>1998</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>139.77863014042</v>
+        <v>141.547288173555</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D80" t="n">
         <v>1998</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>65.6461786335991</v>
+        <v>66.4760632270671</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D81" t="n">
         <v>1998</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F81" t="n">
-        <v>-37.2701541468302</v>
+        <v>-43.4114060887603</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D82" t="n">
         <v>1998</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>22.2547080948462</v>
+        <v>22.4571432799237</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
         <v>14</v>
-      </c>
-      <c r="B83" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" t="s">
-        <v>16</v>
       </c>
       <c r="D83" t="n">
         <v>1999</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F83" t="n">
-        <v>79.9816259924326</v>
+        <v>80.2824005279387</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D84" t="n">
         <v>1999</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F84" t="n">
-        <v>107.952901636936</v>
+        <v>107.814567164016</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D85" t="n">
         <v>1999</v>
       </c>
       <c r="E85" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F85" t="n">
         <v>9.15594840898463</v>
@@ -2164,179 +2150,179 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D86" t="n">
         <v>1999</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>67.8341468607447</v>
+        <v>69.5041626776029</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D87" t="n">
         <v>1999</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F87" t="n">
-        <v>62.9176380730128</v>
+        <v>63.4281157086649</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D88" t="n">
         <v>1999</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F88" t="n">
-        <v>141.979928822096</v>
+        <v>143.698821888542</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D89" t="n">
         <v>1999</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F89" t="n">
-        <v>62.5716251944526</v>
+        <v>63.2025122024995</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D90" t="n">
         <v>1999</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F90" t="n">
-        <v>-42.2162140908723</v>
+        <v>-47.8614369962686</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D91" t="n">
         <v>1999</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F91" t="n">
-        <v>22.4757693630286</v>
+        <v>22.6824936554478</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
         <v>14</v>
-      </c>
-      <c r="B92" t="s">
-        <v>15</v>
-      </c>
-      <c r="C92" t="s">
-        <v>16</v>
       </c>
       <c r="D92" t="n">
         <v>2000</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
-        <v>82.2458235592868</v>
+        <v>82.5268772596401</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D93" t="n">
         <v>2000</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F93" t="n">
-        <v>103.746634446481</v>
+        <v>103.439885186054</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D94" t="n">
         <v>2000</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
         <v>8.28339360029993</v>
@@ -2344,179 +2330,179 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D95" t="n">
         <v>2000</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>66.1567242570252</v>
+        <v>67.9251912915687</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D96" t="n">
         <v>2000</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>62.4668655699026</v>
+        <v>63.0998712786061</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D97" t="n">
         <v>2000</v>
       </c>
       <c r="E97" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>141.738735311043</v>
+        <v>143.516568507755</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D98" t="n">
         <v>2000</v>
       </c>
       <c r="E98" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F98" t="n">
-        <v>62.0408584389983</v>
+        <v>62.6082041483252</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D99" t="n">
         <v>2000</v>
       </c>
       <c r="E99" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F99" t="n">
-        <v>-25.813453448517</v>
+        <v>-35.0525958005019</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D100" t="n">
         <v>2000</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F100" t="n">
-        <v>22.9024050941164</v>
+        <v>23.1138135933001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" t="s">
         <v>14</v>
-      </c>
-      <c r="B101" t="s">
-        <v>15</v>
-      </c>
-      <c r="C101" t="s">
-        <v>16</v>
       </c>
       <c r="D101" t="n">
         <v>2001</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F101" t="n">
-        <v>81.969737200565</v>
+        <v>82.2315432525033</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D102" t="n">
         <v>2001</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F102" t="n">
-        <v>109.081140070161</v>
+        <v>108.581306872232</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D103" t="n">
         <v>2001</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F103" t="n">
         <v>7.992599769047</v>
@@ -2524,179 +2510,179 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D104" t="n">
         <v>2001</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
-        <v>71.2565941817837</v>
+        <v>73.3087360035417</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D105" t="n">
         <v>2001</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F105" t="n">
-        <v>55.9184874921231</v>
+        <v>56.6279064120784</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D106" t="n">
         <v>2001</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F106" t="n">
-        <v>144.461753265182</v>
+        <v>146.108956419883</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D107" t="n">
         <v>2001</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F107" t="n">
-        <v>60.9304428758913</v>
+        <v>61.5806648733439</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D108" t="n">
         <v>2001</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F108" t="n">
-        <v>-39.85631827362</v>
+        <v>-46.8477171146588</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D109" t="n">
         <v>2001</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F109" t="n">
-        <v>23.187451829262</v>
+        <v>23.4040928555574</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
         <v>14</v>
-      </c>
-      <c r="B110" t="s">
-        <v>15</v>
-      </c>
-      <c r="C110" t="s">
-        <v>16</v>
       </c>
       <c r="D110" t="n">
         <v>2002</v>
       </c>
       <c r="E110" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F110" t="n">
-        <v>80.478923061558</v>
+        <v>80.7892356840026</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D111" t="n">
         <v>2002</v>
       </c>
       <c r="E111" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F111" t="n">
-        <v>103.775851545115</v>
+        <v>103.272165165374</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D112" t="n">
         <v>2002</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F112" t="n">
         <v>7.08017418860958</v>
@@ -2704,179 +2690,179 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D113" t="n">
         <v>2002</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F113" t="n">
-        <v>67.2403208622455</v>
+        <v>69.4352575387796</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D114" t="n">
         <v>2002</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F114" t="n">
-        <v>59.1925244958836</v>
+        <v>59.962803530405</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D115" t="n">
         <v>2002</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F115" t="n">
-        <v>145.247910494056</v>
+        <v>147.071949725255</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D116" t="n">
         <v>2002</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F116" t="n">
-        <v>62.2332318615891</v>
+        <v>62.5250332517465</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D117" t="n">
         <v>2002</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F117" t="n">
-        <v>-49.710101337019</v>
+        <v>-52.3222776914196</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D118" t="n">
         <v>2002</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F118" t="n">
-        <v>23.4353264303818</v>
+        <v>23.6564776846818</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" t="s">
         <v>14</v>
-      </c>
-      <c r="B119" t="s">
-        <v>15</v>
-      </c>
-      <c r="C119" t="s">
-        <v>16</v>
       </c>
       <c r="D119" t="n">
         <v>2003</v>
       </c>
       <c r="E119" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F119" t="n">
-        <v>77.222278391617</v>
+        <v>77.4774740649443</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D120" t="n">
         <v>2003</v>
       </c>
       <c r="E120" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F120" t="n">
-        <v>108.473427275109</v>
+        <v>107.975612229585</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D121" t="n">
         <v>2003</v>
       </c>
       <c r="E121" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F121" t="n">
         <v>6.94743726646469</v>
@@ -2884,179 +2870,179 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D122" t="n">
         <v>2003</v>
       </c>
       <c r="E122" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F122" t="n">
-        <v>67.3481760983238</v>
+        <v>69.5688795196053</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D123" t="n">
         <v>2003</v>
       </c>
       <c r="E123" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F123" t="n">
-        <v>62.6333500505122</v>
+        <v>63.4030609587232</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D124" t="n">
         <v>2003</v>
       </c>
       <c r="E124" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F124" t="n">
-        <v>144.633747743584</v>
+        <v>146.526949584758</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D125" t="n">
         <v>2003</v>
       </c>
       <c r="E125" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F125" t="n">
-        <v>62.0317705589047</v>
+        <v>62.2723040833641</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D126" t="n">
         <v>2003</v>
       </c>
       <c r="E126" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F126" t="n">
-        <v>-54.5131452421578</v>
+        <v>-58.2457671946754</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D127" t="n">
         <v>2003</v>
       </c>
       <c r="E127" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F127" t="n">
-        <v>23.5760938137932</v>
+        <v>23.8021853937775</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>12</v>
+      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" t="s">
         <v>14</v>
-      </c>
-      <c r="B128" t="s">
-        <v>15</v>
-      </c>
-      <c r="C128" t="s">
-        <v>16</v>
       </c>
       <c r="D128" t="n">
         <v>2004</v>
       </c>
       <c r="E128" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>77.7412184416691</v>
+        <v>78.0470457708269</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D129" t="n">
         <v>2004</v>
       </c>
       <c r="E129" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F129" t="n">
-        <v>113.071898127343</v>
+        <v>112.636882342497</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D130" t="n">
         <v>2004</v>
       </c>
       <c r="E130" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F130" t="n">
         <v>6.43486160734538</v>
@@ -3064,179 +3050,179 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D131" t="n">
         <v>2004</v>
       </c>
       <c r="E131" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F131" t="n">
-        <v>63.3649450696987</v>
+        <v>65.4791365403302</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D132" t="n">
         <v>2004</v>
       </c>
       <c r="E132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F132" t="n">
-        <v>61.515795240977</v>
+        <v>62.2831967445023</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C133" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D133" t="n">
         <v>2004</v>
       </c>
       <c r="E133" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F133" t="n">
-        <v>144.795856552113</v>
+        <v>146.736866781828</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D134" t="n">
         <v>2004</v>
       </c>
       <c r="E134" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F134" t="n">
-        <v>62.0901841137413</v>
+        <v>62.3428962951301</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D135" t="n">
         <v>2004</v>
       </c>
       <c r="E135" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F135" t="n">
-        <v>-56.4139545728912</v>
+        <v>-59.5099260704479</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D136" t="n">
         <v>2004</v>
       </c>
       <c r="E136" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F136" t="n">
-        <v>23.4298144012886</v>
+        <v>23.6620399264218</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" t="s">
         <v>14</v>
-      </c>
-      <c r="B137" t="s">
-        <v>15</v>
-      </c>
-      <c r="C137" t="s">
-        <v>16</v>
       </c>
       <c r="D137" t="n">
         <v>2005</v>
       </c>
       <c r="E137" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F137" t="n">
-        <v>77.3305665820724</v>
+        <v>77.587122718282</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D138" t="n">
         <v>2005</v>
       </c>
       <c r="E138" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F138" t="n">
-        <v>110.972183836549</v>
+        <v>110.616161363064</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C139" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D139" t="n">
         <v>2005</v>
       </c>
       <c r="E139" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F139" t="n">
         <v>6.07350558625421</v>
@@ -3244,179 +3230,179 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D140" t="n">
         <v>2005</v>
       </c>
       <c r="E140" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F140" t="n">
-        <v>64.8457320572403</v>
+        <v>67.0599956906263</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D141" t="n">
         <v>2005</v>
       </c>
       <c r="E141" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F141" t="n">
-        <v>66.9078911196858</v>
+        <v>67.7143304048408</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D142" t="n">
         <v>2005</v>
       </c>
       <c r="E142" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F142" t="n">
-        <v>142.321988941907</v>
+        <v>144.136943043333</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D143" t="n">
         <v>2005</v>
       </c>
       <c r="E143" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F143" t="n">
-        <v>62.1390858282028</v>
+        <v>62.4259781833322</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D144" t="n">
         <v>2005</v>
       </c>
       <c r="E144" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F144" t="n">
-        <v>-55.5319216042857</v>
+        <v>-60.5450914773372</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C145" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D145" t="n">
         <v>2005</v>
       </c>
       <c r="E145" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F145" t="n">
-        <v>23.2871810134538</v>
+        <v>23.5238243218184</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" t="s">
         <v>14</v>
-      </c>
-      <c r="B146" t="s">
-        <v>15</v>
-      </c>
-      <c r="C146" t="s">
-        <v>16</v>
       </c>
       <c r="D146" t="n">
         <v>2006</v>
       </c>
       <c r="E146" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F146" t="n">
-        <v>76.736115222706</v>
+        <v>76.951806013909</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D147" t="n">
         <v>2006</v>
       </c>
       <c r="E147" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F147" t="n">
-        <v>105.196407116188</v>
+        <v>104.836915712738</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C148" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D148" t="n">
         <v>2006</v>
       </c>
       <c r="E148" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F148" t="n">
         <v>6.26698235068861</v>
@@ -3424,179 +3410,179 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D149" t="n">
         <v>2006</v>
       </c>
       <c r="E149" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F149" t="n">
-        <v>63.7072641096812</v>
+        <v>66.0018377787371</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C150" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D150" t="n">
         <v>2006</v>
       </c>
       <c r="E150" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F150" t="n">
-        <v>62.7334409004444</v>
+        <v>63.5612608750409</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C151" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D151" t="n">
         <v>2006</v>
       </c>
       <c r="E151" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F151" t="n">
-        <v>141.649971989827</v>
+        <v>143.419083268862</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C152" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D152" t="n">
         <v>2006</v>
       </c>
       <c r="E152" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F152" t="n">
-        <v>63.6973839485356</v>
+        <v>63.9539620616576</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C153" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D153" t="n">
         <v>2006</v>
       </c>
       <c r="E153" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F153" t="n">
-        <v>-54.9469120227802</v>
+        <v>-60.3498016074172</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D154" t="n">
         <v>2006</v>
       </c>
       <c r="E154" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F154" t="n">
-        <v>23.2527657559705</v>
+        <v>23.4933299025241</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
+        <v>12</v>
+      </c>
+      <c r="B155" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155" t="s">
         <v>14</v>
-      </c>
-      <c r="B155" t="s">
-        <v>15</v>
-      </c>
-      <c r="C155" t="s">
-        <v>16</v>
       </c>
       <c r="D155" t="n">
         <v>2007</v>
       </c>
       <c r="E155" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F155" t="n">
-        <v>77.2905553567269</v>
+        <v>77.6318103180472</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D156" t="n">
         <v>2007</v>
       </c>
       <c r="E156" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F156" t="n">
-        <v>96.8676836877808</v>
+        <v>96.456965638202</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C157" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D157" t="n">
         <v>2007</v>
       </c>
       <c r="E157" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F157" t="n">
         <v>6.32726824372659</v>
@@ -3604,179 +3590,179 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C158" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D158" t="n">
         <v>2007</v>
       </c>
       <c r="E158" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F158" t="n">
-        <v>62.6491090234908</v>
+        <v>64.924394407675</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C159" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D159" t="n">
         <v>2007</v>
       </c>
       <c r="E159" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F159" t="n">
-        <v>62.3460995403417</v>
+        <v>63.1872150924401</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D160" t="n">
         <v>2007</v>
       </c>
       <c r="E160" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>140.101412835911</v>
+        <v>141.859653226773</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C161" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D161" t="n">
         <v>2007</v>
       </c>
       <c r="E161" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F161" t="n">
-        <v>64.7710936331455</v>
+        <v>65.1929272770515</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C162" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D162" t="n">
         <v>2007</v>
       </c>
       <c r="E162" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F162" t="n">
-        <v>-50.5552710831892</v>
+        <v>-56.4893250061874</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D163" t="n">
         <v>2007</v>
       </c>
       <c r="E163" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F163" t="n">
-        <v>23.1618230534162</v>
+        <v>23.4077178094216</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>12</v>
+      </c>
+      <c r="B164" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" t="s">
         <v>14</v>
-      </c>
-      <c r="B164" t="s">
-        <v>15</v>
-      </c>
-      <c r="C164" t="s">
-        <v>16</v>
       </c>
       <c r="D164" t="n">
         <v>2008</v>
       </c>
       <c r="E164" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F164" t="n">
-        <v>78.9979407360478</v>
+        <v>79.279625744531</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C165" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D165" t="n">
         <v>2008</v>
       </c>
       <c r="E165" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F165" t="n">
-        <v>103.773200948933</v>
+        <v>103.318299940211</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C166" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D166" t="n">
         <v>2008</v>
       </c>
       <c r="E166" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F166" t="n">
         <v>6.6016527905733</v>
@@ -3784,179 +3770,179 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C167" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D167" t="n">
         <v>2008</v>
       </c>
       <c r="E167" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F167" t="n">
-        <v>60.7396610386843</v>
+        <v>63.0172399273258</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C168" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D168" t="n">
         <v>2008</v>
       </c>
       <c r="E168" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F168" t="n">
-        <v>61.2059324702593</v>
+        <v>61.9961633392619</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C169" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D169" t="n">
         <v>2008</v>
       </c>
       <c r="E169" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F169" t="n">
-        <v>133.697276539309</v>
+        <v>135.440430694221</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C170" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D170" t="n">
         <v>2008</v>
       </c>
       <c r="E170" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F170" t="n">
-        <v>60.497239305079</v>
+        <v>60.8485853548925</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C171" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D171" t="n">
         <v>2008</v>
       </c>
       <c r="E171" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F171" t="n">
-        <v>-49.4428398392252</v>
+        <v>-55.2048065881418</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C172" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D172" t="n">
         <v>2008</v>
       </c>
       <c r="E172" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F172" t="n">
-        <v>23.2790886283747</v>
+        <v>23.5311148156356</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
+        <v>12</v>
+      </c>
+      <c r="B173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" t="s">
         <v>14</v>
-      </c>
-      <c r="B173" t="s">
-        <v>15</v>
-      </c>
-      <c r="C173" t="s">
-        <v>16</v>
       </c>
       <c r="D173" t="n">
         <v>2009</v>
       </c>
       <c r="E173" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F173" t="n">
-        <v>77.9083940012464</v>
+        <v>78.1423346601839</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D174" t="n">
         <v>2009</v>
       </c>
       <c r="E174" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F174" t="n">
-        <v>106.013818163033</v>
+        <v>105.32019791102</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C175" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D175" t="n">
         <v>2009</v>
       </c>
       <c r="E175" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F175" t="n">
         <v>6.3159274690341</v>
@@ -3964,179 +3950,179 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C176" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D176" t="n">
         <v>2009</v>
       </c>
       <c r="E176" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>51.9896962066283</v>
+        <v>54.5832723242342</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C177" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D177" t="n">
         <v>2009</v>
       </c>
       <c r="E177" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F177" t="n">
-        <v>59.3995143063828</v>
+        <v>60.2022686507108</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D178" t="n">
         <v>2009</v>
       </c>
       <c r="E178" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F178" t="n">
-        <v>133.160298215631</v>
+        <v>134.836635725665</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C179" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D179" t="n">
         <v>2009</v>
       </c>
       <c r="E179" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F179" t="n">
-        <v>50.4390852023167</v>
+        <v>50.7576572588075</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D180" t="n">
         <v>2009</v>
       </c>
       <c r="E180" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F180" t="n">
-        <v>-37.7429159965038</v>
+        <v>-43.8634377930238</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C181" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D181" t="n">
         <v>2009</v>
       </c>
       <c r="E181" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F181" t="n">
-        <v>22.735351137752</v>
+        <v>23.0039499384242</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" t="s">
         <v>14</v>
-      </c>
-      <c r="B182" t="s">
-        <v>15</v>
-      </c>
-      <c r="C182" t="s">
-        <v>16</v>
       </c>
       <c r="D182" t="n">
         <v>2010</v>
       </c>
       <c r="E182" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F182" t="n">
-        <v>75.7464060356602</v>
+        <v>75.9721303484875</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C183" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D183" t="n">
         <v>2010</v>
       </c>
       <c r="E183" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F183" t="n">
-        <v>104.003505978213</v>
+        <v>103.35778331139</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D184" t="n">
         <v>2010</v>
       </c>
       <c r="E184" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F184" t="n">
         <v>5.97514245969458</v>
@@ -4144,179 +4130,179 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D185" t="n">
         <v>2010</v>
       </c>
       <c r="E185" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F185" t="n">
-        <v>55.4984930995053</v>
+        <v>58.5445811646501</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C186" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D186" t="n">
         <v>2010</v>
       </c>
       <c r="E186" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F186" t="n">
-        <v>60.0628304593506</v>
+        <v>60.7401037241964</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D187" t="n">
         <v>2010</v>
       </c>
       <c r="E187" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F187" t="n">
-        <v>133.939047842432</v>
+        <v>135.658378181615</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C188" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D188" t="n">
         <v>2010</v>
       </c>
       <c r="E188" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F188" t="n">
-        <v>53.6017068587333</v>
+        <v>54.1708395931434</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C189" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D189" t="n">
         <v>2010</v>
       </c>
       <c r="E189" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F189" t="n">
-        <v>-39.7884126279913</v>
+        <v>-46.2576935229718</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C190" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D190" t="n">
         <v>2010</v>
       </c>
       <c r="E190" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F190" t="n">
-        <v>22.9209432963209</v>
+        <v>23.2221011552844</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
+        <v>12</v>
+      </c>
+      <c r="B191" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" t="s">
         <v>14</v>
-      </c>
-      <c r="B191" t="s">
-        <v>15</v>
-      </c>
-      <c r="C191" t="s">
-        <v>16</v>
       </c>
       <c r="D191" t="n">
         <v>2011</v>
       </c>
       <c r="E191" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F191" t="n">
-        <v>75.4401148469661</v>
+        <v>75.646537191015</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D192" t="n">
         <v>2011</v>
       </c>
       <c r="E192" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F192" t="n">
-        <v>88.176269228581</v>
+        <v>87.2695858069342</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C193" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D193" t="n">
         <v>2011</v>
       </c>
       <c r="E193" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F193" t="n">
         <v>5.64416240306759</v>
@@ -4324,179 +4310,179 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D194" t="n">
         <v>2011</v>
       </c>
       <c r="E194" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F194" t="n">
-        <v>52.8909259015991</v>
+        <v>55.7380936342212</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C195" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D195" t="n">
         <v>2011</v>
       </c>
       <c r="E195" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F195" t="n">
-        <v>54.7215319647701</v>
+        <v>55.4153210751627</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C196" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D196" t="n">
         <v>2011</v>
       </c>
       <c r="E196" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F196" t="n">
-        <v>135.113579280588</v>
+        <v>136.838276033599</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D197" t="n">
         <v>2011</v>
       </c>
       <c r="E197" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F197" t="n">
-        <v>53.1898389291634</v>
+        <v>53.9787761137922</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C198" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D198" t="n">
         <v>2011</v>
       </c>
       <c r="E198" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F198" t="n">
-        <v>-41.0186416858865</v>
+        <v>-46.5002551606898</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C199" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D199" t="n">
         <v>2011</v>
       </c>
       <c r="E199" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F199" t="n">
-        <v>21.9489681982606</v>
+        <v>22.2748356916258</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>12</v>
+      </c>
+      <c r="B200" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" t="s">
         <v>14</v>
-      </c>
-      <c r="B200" t="s">
-        <v>15</v>
-      </c>
-      <c r="C200" t="s">
-        <v>16</v>
       </c>
       <c r="D200" t="n">
         <v>2012</v>
       </c>
       <c r="E200" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F200" t="n">
-        <v>75.1704947189626</v>
+        <v>75.4228280497207</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C201" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D201" t="n">
         <v>2012</v>
       </c>
       <c r="E201" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F201" t="n">
-        <v>95.0845555367682</v>
+        <v>94.2201247962619</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C202" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D202" t="n">
         <v>2012</v>
       </c>
       <c r="E202" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F202" t="n">
         <v>5.014522126582</v>
@@ -4504,179 +4490,179 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C203" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D203" t="n">
         <v>2012</v>
       </c>
       <c r="E203" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F203" t="n">
-        <v>51.4319772952801</v>
+        <v>54.2534720213975</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C204" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D204" t="n">
         <v>2012</v>
       </c>
       <c r="E204" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F204" t="n">
-        <v>56.9794778883763</v>
+        <v>57.662131506679</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C205" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D205" t="n">
         <v>2012</v>
       </c>
       <c r="E205" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F205" t="n">
-        <v>133.435283050519</v>
+        <v>135.173996874273</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C206" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D206" t="n">
         <v>2012</v>
       </c>
       <c r="E206" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F206" t="n">
-        <v>51.0828320366343</v>
+        <v>51.9211415451992</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C207" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D207" t="n">
         <v>2012</v>
       </c>
       <c r="E207" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F207" t="n">
-        <v>-44.2543792925874</v>
+        <v>-50.6813350477766</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C208" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D208" t="n">
         <v>2012</v>
       </c>
       <c r="E208" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>21.5213255252897</v>
+        <v>21.8687601121151</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
+        <v>12</v>
+      </c>
+      <c r="B209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" t="s">
         <v>14</v>
-      </c>
-      <c r="B209" t="s">
-        <v>15</v>
-      </c>
-      <c r="C209" t="s">
-        <v>16</v>
       </c>
       <c r="D209" t="n">
         <v>2013</v>
       </c>
       <c r="E209" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F209" t="n">
-        <v>74.3191338975337</v>
+        <v>74.5562003304531</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C210" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D210" t="n">
         <v>2013</v>
       </c>
       <c r="E210" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F210" t="n">
-        <v>97.9966368455951</v>
+        <v>97.0419916241627</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C211" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D211" t="n">
         <v>2013</v>
       </c>
       <c r="E211" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F211" t="n">
         <v>4.6913395559592</v>
@@ -4684,179 +4670,179 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C212" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D212" t="n">
         <v>2013</v>
       </c>
       <c r="E212" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F212" t="n">
-        <v>50.8990319414421</v>
+        <v>54.3782787794737</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C213" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D213" t="n">
         <v>2013</v>
       </c>
       <c r="E213" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F213" t="n">
-        <v>55.3374033777215</v>
+        <v>56.0274237047267</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C214" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D214" t="n">
         <v>2013</v>
       </c>
       <c r="E214" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F214" t="n">
-        <v>133.060235786416</v>
+        <v>134.782281905084</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C215" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D215" t="n">
         <v>2013</v>
       </c>
       <c r="E215" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F215" t="n">
-        <v>52.8353207121706</v>
+        <v>53.8977783873859</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C216" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D216" t="n">
         <v>2013</v>
       </c>
       <c r="E216" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F216" t="n">
-        <v>-50.2468404405747</v>
+        <v>-55.6150846355742</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C217" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D217" t="n">
         <v>2013</v>
       </c>
       <c r="E217" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F217" t="n">
-        <v>19.6960274849752</v>
+        <v>20.0595936207816</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
+        <v>12</v>
+      </c>
+      <c r="B218" t="s">
+        <v>13</v>
+      </c>
+      <c r="C218" t="s">
         <v>14</v>
-      </c>
-      <c r="B218" t="s">
-        <v>15</v>
-      </c>
-      <c r="C218" t="s">
-        <v>16</v>
       </c>
       <c r="D218" t="n">
         <v>2014</v>
       </c>
       <c r="E218" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F218" t="n">
-        <v>75.9333741697374</v>
+        <v>76.2284942976944</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C219" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D219" t="n">
         <v>2014</v>
       </c>
       <c r="E219" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F219" t="n">
-        <v>81.3001831395176</v>
+        <v>80.1353236562963</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C220" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D220" t="n">
         <v>2014</v>
       </c>
       <c r="E220" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F220" t="n">
         <v>4.43834940594229</v>
@@ -4864,179 +4850,179 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C221" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D221" t="n">
         <v>2014</v>
       </c>
       <c r="E221" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F221" t="n">
-        <v>48.2912299283605</v>
+        <v>52.8296690163577</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C222" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D222" t="n">
         <v>2014</v>
       </c>
       <c r="E222" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F222" t="n">
-        <v>42.0585245744597</v>
+        <v>42.7839924375099</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C223" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D223" t="n">
         <v>2014</v>
       </c>
       <c r="E223" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F223" t="n">
-        <v>132.614533750446</v>
+        <v>134.272079250654</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C224" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D224" t="n">
         <v>2014</v>
       </c>
       <c r="E224" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>52.2911910474955</v>
+        <v>53.5641286831943</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C225" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D225" t="n">
         <v>2014</v>
       </c>
       <c r="E225" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F225" t="n">
-        <v>-42.7726564366173</v>
+        <v>-47.5131551771733</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C226" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D226" t="n">
         <v>2014</v>
       </c>
       <c r="E226" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F226" t="n">
-        <v>18.9332217665725</v>
+        <v>19.3138294613224</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227" t="s">
+        <v>13</v>
+      </c>
+      <c r="C227" t="s">
         <v>14</v>
-      </c>
-      <c r="B227" t="s">
-        <v>15</v>
-      </c>
-      <c r="C227" t="s">
-        <v>16</v>
       </c>
       <c r="D227" t="n">
         <v>2015</v>
       </c>
       <c r="E227" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F227" t="n">
-        <v>75.5610473628596</v>
+        <v>76.0329413278424</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C228" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D228" t="n">
         <v>2015</v>
       </c>
       <c r="E228" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F228" t="n">
-        <v>84.4617277660407</v>
+        <v>83.4852834151156</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C229" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D229" t="n">
         <v>2015</v>
       </c>
       <c r="E229" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F229" t="n">
         <v>4.3121225386273</v>
@@ -5044,179 +5030,179 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C230" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D230" t="n">
         <v>2015</v>
       </c>
       <c r="E230" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F230" t="n">
-        <v>47.1230058102641</v>
+        <v>51.3869232564657</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C231" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D231" t="n">
         <v>2015</v>
       </c>
       <c r="E231" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F231" t="n">
-        <v>44.9585505514436</v>
+        <v>45.6691178062559</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C232" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D232" t="n">
         <v>2015</v>
       </c>
       <c r="E232" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F232" t="n">
-        <v>134.147922137728</v>
+        <v>135.801126321094</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C233" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D233" t="n">
         <v>2015</v>
       </c>
       <c r="E233" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F233" t="n">
-        <v>50.7820732958225</v>
+        <v>52.1194086019056</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C234" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D234" t="n">
         <v>2015</v>
       </c>
       <c r="E234" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F234" t="n">
-        <v>-39.6581494729417</v>
+        <v>-44.7272704762167</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C235" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D235" t="n">
         <v>2015</v>
       </c>
       <c r="E235" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F235" t="n">
-        <v>17.9270438636689</v>
+        <v>18.3222735534489</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" t="s">
+        <v>13</v>
+      </c>
+      <c r="C236" t="s">
         <v>14</v>
-      </c>
-      <c r="B236" t="s">
-        <v>15</v>
-      </c>
-      <c r="C236" t="s">
-        <v>16</v>
       </c>
       <c r="D236" t="n">
         <v>2016</v>
       </c>
       <c r="E236" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F236" t="n">
-        <v>74.6881268923876</v>
+        <v>75.0337849506519</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C237" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D237" t="n">
         <v>2016</v>
       </c>
       <c r="E237" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F237" t="n">
-        <v>84.3623563361187</v>
+        <v>83.5830777770005</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C238" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D238" t="n">
         <v>2016</v>
       </c>
       <c r="E238" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F238" t="n">
         <v>4.35002764884879</v>
@@ -5224,179 +5210,179 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C239" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D239" t="n">
         <v>2016</v>
       </c>
       <c r="E239" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F239" t="n">
-        <v>46.744106918773</v>
+        <v>51.6068549129556</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C240" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D240" t="n">
         <v>2016</v>
       </c>
       <c r="E240" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F240" t="n">
-        <v>48.5109590654436</v>
+        <v>49.2608965980216</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C241" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D241" t="n">
         <v>2016</v>
       </c>
       <c r="E241" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F241" t="n">
-        <v>134.532429096959</v>
+        <v>136.256085388565</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C242" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D242" t="n">
         <v>2016</v>
       </c>
       <c r="E242" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F242" t="n">
-        <v>50.5489154638566</v>
+        <v>52.2301517064858</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C243" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D243" t="n">
         <v>2016</v>
       </c>
       <c r="E243" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F243" t="n">
-        <v>-35.8696980595475</v>
+        <v>-38.6347624698217</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C244" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D244" t="n">
         <v>2016</v>
       </c>
       <c r="E244" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F244" t="n">
-        <v>17.9824189289402</v>
+        <v>18.3998168829136</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
+        <v>12</v>
+      </c>
+      <c r="B245" t="s">
+        <v>13</v>
+      </c>
+      <c r="C245" t="s">
         <v>14</v>
-      </c>
-      <c r="B245" t="s">
-        <v>15</v>
-      </c>
-      <c r="C245" t="s">
-        <v>16</v>
       </c>
       <c r="D245" t="n">
         <v>2017</v>
       </c>
       <c r="E245" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F245" t="n">
-        <v>74.7684142574473</v>
+        <v>74.8086895012716</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C246" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D246" t="n">
         <v>2017</v>
       </c>
       <c r="E246" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F246" t="n">
-        <v>83.9065224506939</v>
+        <v>82.8067727664014</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C247" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D247" t="n">
         <v>2017</v>
       </c>
       <c r="E247" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F247" t="n">
         <v>4.18803853821803</v>
@@ -5404,179 +5390,179 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C248" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D248" t="n">
         <v>2017</v>
       </c>
       <c r="E248" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F248" t="n">
-        <v>44.6353508293385</v>
+        <v>49.8509318804622</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C249" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D249" t="n">
         <v>2017</v>
       </c>
       <c r="E249" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F249" t="n">
-        <v>52.4438374363841</v>
+        <v>53.1330693627435</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C250" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D250" t="n">
         <v>2017</v>
       </c>
       <c r="E250" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F250" t="n">
-        <v>134.441070757011</v>
+        <v>136.172059185812</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C251" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D251" t="n">
         <v>2017</v>
       </c>
       <c r="E251" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F251" t="n">
-        <v>51.7801508924817</v>
+        <v>53.6715980682025</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C252" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D252" t="n">
         <v>2017</v>
       </c>
       <c r="E252" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F252" t="n">
-        <v>-28.1030613662161</v>
+        <v>-31.8500785058791</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C253" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D253" t="n">
         <v>2017</v>
       </c>
       <c r="E253" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F253" t="n">
-        <v>18.0247958080737</v>
+        <v>18.4554597978431</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
+        <v>12</v>
+      </c>
+      <c r="B254" t="s">
+        <v>13</v>
+      </c>
+      <c r="C254" t="s">
         <v>14</v>
-      </c>
-      <c r="B254" t="s">
-        <v>15</v>
-      </c>
-      <c r="C254" t="s">
-        <v>16</v>
       </c>
       <c r="D254" t="n">
         <v>2018</v>
       </c>
       <c r="E254" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F254" t="n">
-        <v>73.7489179471165</v>
+        <v>73.6989616236482</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C255" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D255" t="n">
         <v>2018</v>
       </c>
       <c r="E255" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F255" t="n">
-        <v>80.8515182418409</v>
+        <v>79.1574940061693</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C256" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D256" t="n">
         <v>2018</v>
       </c>
       <c r="E256" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F256" t="n">
         <v>4.22505632354894</v>
@@ -5584,1022 +5570,1202 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C257" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D257" t="n">
         <v>2018</v>
       </c>
       <c r="E257" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F257" t="n">
-        <v>44.4221721596285</v>
+        <v>50.2151426164467</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C258" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D258" t="n">
         <v>2018</v>
       </c>
       <c r="E258" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F258" t="n">
-        <v>43.0002918301782</v>
+        <v>43.7226558650751</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C259" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D259" t="n">
         <v>2018</v>
       </c>
       <c r="E259" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F259" t="n">
-        <v>131.859569162346</v>
+        <v>133.64226681733</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C260" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D260" t="n">
         <v>2018</v>
       </c>
       <c r="E260" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F260" t="n">
-        <v>49.0676566036752</v>
+        <v>51.1061455693387</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C261" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D261" t="n">
         <v>2018</v>
       </c>
       <c r="E261" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F261" t="n">
-        <v>-38.1576623490659</v>
+        <v>-47.9447179730835</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C262" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D262" t="n">
         <v>2018</v>
       </c>
       <c r="E262" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F262" t="n">
-        <v>17.7677382667462</v>
+        <v>18.2133958550352</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
+        <v>12</v>
+      </c>
+      <c r="B263" t="s">
+        <v>13</v>
+      </c>
+      <c r="C263" t="s">
         <v>14</v>
-      </c>
-      <c r="B263" t="s">
-        <v>15</v>
-      </c>
-      <c r="C263" t="s">
-        <v>16</v>
       </c>
       <c r="D263" t="n">
         <v>2019</v>
       </c>
       <c r="E263" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F263" t="n">
-        <v>72.0207188739168</v>
+        <v>72.6309737625109</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C264" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D264" t="n">
         <v>2019</v>
       </c>
       <c r="E264" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F264" t="n">
-        <v>78.6156488611831</v>
+        <v>76.795621429228</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C265" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D265" t="n">
         <v>2019</v>
       </c>
       <c r="E265" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F265" t="n">
-        <v>3.72408851264545</v>
+        <v>3.72419444264545</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C266" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D266" t="n">
         <v>2019</v>
       </c>
       <c r="E266" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F266" t="n">
-        <v>43.2304402395394</v>
+        <v>49.3603745825714</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C267" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D267" t="n">
         <v>2019</v>
       </c>
       <c r="E267" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F267" t="n">
-        <v>41.6347095542551</v>
+        <v>42.30238554829</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C268" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D268" t="n">
         <v>2019</v>
       </c>
       <c r="E268" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F268" t="n">
-        <v>131.114040729454</v>
+        <v>132.832371796078</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C269" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D269" t="n">
         <v>2019</v>
       </c>
       <c r="E269" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F269" t="n">
-        <v>45.9208401634258</v>
+        <v>47.8731224670518</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C270" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D270" t="n">
         <v>2019</v>
       </c>
       <c r="E270" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F270" t="n">
-        <v>-35.0238950756398</v>
+        <v>-41.8614164599693</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C271" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D271" t="n">
         <v>2019</v>
       </c>
       <c r="E271" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F271" t="n">
-        <v>18.9973866505008</v>
+        <v>19.4204308774972</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
+        <v>12</v>
+      </c>
+      <c r="B272" t="s">
+        <v>13</v>
+      </c>
+      <c r="C272" t="s">
         <v>14</v>
-      </c>
-      <c r="B272" t="s">
-        <v>15</v>
-      </c>
-      <c r="C272" t="s">
-        <v>16</v>
       </c>
       <c r="D272" t="n">
         <v>2020</v>
       </c>
       <c r="E272" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F272" t="n">
-        <v>70.4425645060045</v>
+        <v>71.3938605096517</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C273" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D273" t="n">
         <v>2020</v>
       </c>
       <c r="E273" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F273" t="n">
-        <v>75.9601588439139</v>
+        <v>74.4450145953872</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C274" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D274" t="n">
         <v>2020</v>
       </c>
       <c r="E274" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F274" t="n">
-        <v>3.16101014591269</v>
+        <v>3.1612755437187</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C275" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D275" t="n">
         <v>2020</v>
       </c>
       <c r="E275" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F275" t="n">
-        <v>39.5961628143534</v>
+        <v>45.040488247059</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C276" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D276" t="n">
         <v>2020</v>
       </c>
       <c r="E276" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F276" t="n">
-        <v>37.221441628401</v>
+        <v>37.8138761274945</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C277" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D277" t="n">
         <v>2020</v>
       </c>
       <c r="E277" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F277" t="n">
-        <v>110.233309935805</v>
+        <v>111.746860749817</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C278" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D278" t="n">
         <v>2020</v>
       </c>
       <c r="E278" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F278" t="n">
-        <v>39.9039187645987</v>
+        <v>41.7747260129653</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C279" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D279" t="n">
         <v>2020</v>
       </c>
       <c r="E279" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F279" t="n">
-        <v>-37.7427153455393</v>
+        <v>-48.2789707488106</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C280" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D280" t="n">
         <v>2020</v>
       </c>
       <c r="E280" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F280" t="n">
-        <v>18.7273993539039</v>
+        <v>19.1521693548393</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
+        <v>12</v>
+      </c>
+      <c r="B281" t="s">
+        <v>13</v>
+      </c>
+      <c r="C281" t="s">
         <v>14</v>
-      </c>
-      <c r="B281" t="s">
-        <v>15</v>
-      </c>
-      <c r="C281" t="s">
-        <v>16</v>
       </c>
       <c r="D281" t="n">
         <v>2021</v>
       </c>
       <c r="E281" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F281" t="n">
-        <v>69.7048182142132</v>
+        <v>70.8205586327331</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C282" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D282" t="n">
         <v>2021</v>
       </c>
       <c r="E282" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F282" t="n">
-        <v>79.2747103643222</v>
+        <v>78.0480382258714</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C283" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D283" t="n">
         <v>2021</v>
       </c>
       <c r="E283" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F283" t="n">
-        <v>2.6902018113239</v>
+        <v>2.69078075210104</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C284" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D284" t="n">
         <v>2021</v>
       </c>
       <c r="E284" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F284" t="n">
-        <v>42.5072672700771</v>
+        <v>47.5659387960282</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B285" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C285" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D285" t="n">
         <v>2021</v>
       </c>
       <c r="E285" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F285" t="n">
-        <v>39.7916230959319</v>
+        <v>40.436069046383</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B286" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C286" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D286" t="n">
         <v>2021</v>
       </c>
       <c r="E286" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F286" t="n">
-        <v>124.342736000748</v>
+        <v>125.883167681656</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B287" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C287" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D287" t="n">
         <v>2021</v>
       </c>
       <c r="E287" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F287" t="n">
-        <v>42.2269139766652</v>
+        <v>44.1130759942825</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B288" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C288" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D288" t="n">
         <v>2021</v>
       </c>
       <c r="E288" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F288" t="n">
-        <v>-34.9593823467225</v>
+        <v>-39.7225461202484</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C289" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D289" t="n">
         <v>2021</v>
       </c>
       <c r="E289" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F289" t="n">
-        <v>18.4318961120163</v>
+        <v>18.8482189163529</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
+        <v>12</v>
+      </c>
+      <c r="B290" t="s">
+        <v>13</v>
+      </c>
+      <c r="C290" t="s">
         <v>14</v>
-      </c>
-      <c r="B290" t="s">
-        <v>15</v>
-      </c>
-      <c r="C290" t="s">
-        <v>16</v>
       </c>
       <c r="D290" t="n">
         <v>2022</v>
       </c>
       <c r="E290" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F290" t="n">
-        <v>66.8566388724123</v>
+        <v>68.3563458994671</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C291" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D291" t="n">
         <v>2022</v>
       </c>
       <c r="E291" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F291" t="n">
-        <v>67.9908003480637</v>
+        <v>66.1340253555937</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C292" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D292" t="n">
         <v>2022</v>
       </c>
       <c r="E292" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F292" t="n">
-        <v>2.52233774065143</v>
+        <v>2.52283758142669</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C293" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D293" t="n">
         <v>2022</v>
       </c>
       <c r="E293" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F293" t="n">
-        <v>39.0550598836006</v>
+        <v>43.8094089460566</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C294" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D294" t="n">
         <v>2022</v>
       </c>
       <c r="E294" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F294" t="n">
-        <v>40.922297153792</v>
+        <v>42.1251196823898</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B295" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C295" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D295" t="n">
         <v>2022</v>
       </c>
       <c r="E295" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F295" t="n">
-        <v>128.634788964131</v>
+        <v>130.282216814154</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C296" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D296" t="n">
         <v>2022</v>
       </c>
       <c r="E296" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F296" t="n">
-        <v>38.257012701314</v>
+        <v>40.2490753579717</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C297" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D297" t="n">
         <v>2022</v>
       </c>
       <c r="E297" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F297" t="n">
-        <v>-33.9704439400604</v>
+        <v>-38.7215979719134</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C298" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D298" t="n">
         <v>2022</v>
       </c>
       <c r="E298" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F298" t="n">
-        <v>18.3501808597778</v>
+        <v>18.835824234252</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
+        <v>12</v>
+      </c>
+      <c r="B299" t="s">
+        <v>13</v>
+      </c>
+      <c r="C299" t="s">
         <v>14</v>
-      </c>
-      <c r="B299" t="s">
-        <v>15</v>
-      </c>
-      <c r="C299" t="s">
-        <v>16</v>
       </c>
       <c r="D299" t="n">
         <v>2023</v>
       </c>
       <c r="E299" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F299" t="n">
-        <v>66.3910819360491</v>
+        <v>67.650085912739</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B300" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C300" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D300" t="n">
         <v>2023</v>
       </c>
       <c r="E300" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F300" t="n">
-        <v>61.0805853106381</v>
+        <v>60.7369026688046</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C301" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D301" t="n">
         <v>2023</v>
       </c>
       <c r="E301" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F301" t="n">
-        <v>2.43770659270764</v>
+        <v>2.43962291607739</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B302" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C302" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D302" t="n">
         <v>2023</v>
       </c>
       <c r="E302" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F302" t="n">
-        <v>35.9346508281061</v>
+        <v>40.0586606355787</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B303" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C303" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D303" t="n">
         <v>2023</v>
       </c>
       <c r="E303" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F303" t="n">
-        <v>34.0172463863685</v>
+        <v>34.4003239814899</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B304" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C304" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D304" t="n">
         <v>2023</v>
       </c>
       <c r="E304" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F304" t="n">
-        <v>123.430542406095</v>
+        <v>125.044188208844</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B305" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C305" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D305" t="n">
         <v>2023</v>
       </c>
       <c r="E305" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F305" t="n">
-        <v>34.1027345578582</v>
+        <v>35.8376320119552</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B306" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C306" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D306" t="n">
         <v>2023</v>
       </c>
       <c r="E306" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F306" t="n">
-        <v>-37.3805506121324</v>
+        <v>-38.6673471179046</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B307" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C307" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D307" t="n">
         <v>2023</v>
       </c>
       <c r="E307" t="s">
+        <v>15</v>
+      </c>
+      <c r="F307" t="n">
+        <v>18.6492108034999</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>12</v>
+      </c>
+      <c r="B308" t="s">
+        <v>13</v>
+      </c>
+      <c r="C308" t="s">
+        <v>14</v>
+      </c>
+      <c r="D308" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E308" t="s">
+        <v>15</v>
+      </c>
+      <c r="F308" t="n">
+        <v>67.0657388954523</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>12</v>
+      </c>
+      <c r="B309" t="s">
+        <v>13</v>
+      </c>
+      <c r="C309" t="s">
+        <v>16</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E309" t="s">
+        <v>15</v>
+      </c>
+      <c r="F309" t="n">
+        <v>60.198095029135</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>12</v>
+      </c>
+      <c r="B310" t="s">
+        <v>13</v>
+      </c>
+      <c r="C310" t="s">
         <v>17</v>
       </c>
-      <c r="F307" t="n">
-        <v>18.2024973386844</v>
+      <c r="D310" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E310" t="s">
+        <v>15</v>
+      </c>
+      <c r="F310" t="n">
+        <v>2.22794231745335</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>12</v>
+      </c>
+      <c r="B311" t="s">
+        <v>13</v>
+      </c>
+      <c r="C311" t="s">
+        <v>18</v>
+      </c>
+      <c r="D311" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E311" t="s">
+        <v>15</v>
+      </c>
+      <c r="F311" t="n">
+        <v>37.000947386231</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>12</v>
+      </c>
+      <c r="B312" t="s">
+        <v>13</v>
+      </c>
+      <c r="C312" t="s">
+        <v>19</v>
+      </c>
+      <c r="D312" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E312" t="s">
+        <v>15</v>
+      </c>
+      <c r="F312" t="n">
+        <v>29.172602126453</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>12</v>
+      </c>
+      <c r="B313" t="s">
+        <v>13</v>
+      </c>
+      <c r="C313" t="s">
+        <v>20</v>
+      </c>
+      <c r="D313" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E313" t="s">
+        <v>15</v>
+      </c>
+      <c r="F313" t="n">
+        <v>123.516115468459</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>12</v>
+      </c>
+      <c r="B314" t="s">
+        <v>13</v>
+      </c>
+      <c r="C314" t="s">
+        <v>21</v>
+      </c>
+      <c r="D314" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E314" t="s">
+        <v>15</v>
+      </c>
+      <c r="F314" t="n">
+        <v>33.5868595231281</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>12</v>
+      </c>
+      <c r="B315" t="s">
+        <v>13</v>
+      </c>
+      <c r="C315" t="s">
+        <v>22</v>
+      </c>
+      <c r="D315" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E315" t="s">
+        <v>15</v>
+      </c>
+      <c r="F315" t="n">
+        <v>-40.5246321677622</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>12</v>
+      </c>
+      <c r="B316" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316" t="s">
+        <v>23</v>
+      </c>
+      <c r="D316" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E316" t="s">
+        <v>15</v>
+      </c>
+      <c r="F316" t="n">
+        <v>18.3428848968512</v>
       </c>
     </row>
   </sheetData>

--- a/plots/countries/sectors/France-sectors.xlsx
+++ b/plots/countries/sectors/France-sectors.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2.1) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
